--- a/etc/hebrew/directions.xlsx
+++ b/etc/hebrew/directions.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -580,6 +580,90 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>north</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>צָפוֹן</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>דָּרוֹם</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>east</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>מִזְרָח</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>west</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>מַעֲרָב</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
